--- a/sales data analytics.xlsx
+++ b/sales data analytics.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaviyarasan\Documents\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55359CB1-8B0C-482A-A7CD-0E7079C646F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B0B6B3-8EE6-4093-A893-FF960C6520CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{A5E7FF8B-4895-47B1-A176-FC95B8303529}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{A5E7FF8B-4895-47B1-A176-FC95B8303529}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Data" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Region">#N/A</definedName>
@@ -23,14 +24,14 @@
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId4"/>
-    <pivotCache cacheId="4" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId6"/>
         <x14:slicerCache r:id="rId7"/>
+        <x14:slicerCache r:id="rId8"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="73">
   <si>
     <t>Product</t>
   </si>
@@ -283,15 +284,28 @@
   <si>
     <t>Sum of Net Revenue</t>
   </si>
+  <si>
+    <t>Sales Dashboard</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>Total Orders</t>
+  </si>
+  <si>
+    <t>Best Product</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="\₹#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,8 +343,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -358,6 +396,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,7 +446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -429,41 +485,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{42637416-F14A-47AA-A475-9C26C34017FD}"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color rgb="FF002060"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0%"/>
       <fill>
@@ -692,6 +742,30 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color rgb="FF002060"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -979,7 +1053,7 @@
                   <c:v>Camera</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Laptop</c:v>
+                  <c:v>Headphones</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Mobile</c:v>
@@ -1006,25 +1080,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>735265.53099999996</c:v>
+                  <c:v>101904.72</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>710439.80149999994</c:v>
+                  <c:v>59448.152499999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>479394.96600000001</c:v>
+                  <c:v>23085.599999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>465530.99349999998</c:v>
+                  <c:v>60581.993999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>496676.63049999997</c:v>
+                  <c:v>156457.41899999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51001.686499999996</c:v>
+                  <c:v>99288.382000000012</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>463763.58</c:v>
+                  <c:v>151079</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2550,6 +2624,1209 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[sales data analytics.xlsx]Sheet1!PivotTable15</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue by Product - 2024</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:sysClr val="window" lastClr="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="25000"/>
+                  <a:lumOff val="75000"/>
+                </a:sysClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-F0E9-4764-B052-FB17D56CF466}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-F0E9-4764-B052-FB17D56CF466}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-F0E9-4764-B052-FB17D56CF466}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-F0E9-4764-B052-FB17D56CF466}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="rect">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-F0E9-4764-B052-FB17D56CF466}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-F0E9-4764-B052-FB17D56CF466}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-F0E9-4764-B052-FB17D56CF466}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-F0E9-4764-B052-FB17D56CF466}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="rect">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Camera</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Headphones</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mobile</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Smartwatch</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Speaker</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$4:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>101904.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>59448.152499999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23085.599999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60581.993999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>156457.41899999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>99288.382000000012</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>151079</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-63FA-40C4-811D-B3D3A8C14FBC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="933826447"/>
+        <c:axId val="176328623"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="933826447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="176328623"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="176328623"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="933826447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2710,6 +3987,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -4384,6 +5701,509 @@
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4897,18 +6717,18 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>373380</xdr:colOff>
+      <xdr:colOff>68580</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1165860</xdr:colOff>
+      <xdr:colOff>861060</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>112395</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Region">
@@ -4931,7 +6751,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4941,7 +6761,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="373380" y="2392680"/>
+              <a:off x="68580" y="2400300"/>
               <a:ext cx="1828800" cy="2466975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5047,8 +6867,123 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A239984D-8C72-051C-6CF3-086134ABEFED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>157480</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>40640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>233680</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Region 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EB2ECF9-03C7-E835-746A-71C78D0D738E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Region 2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8181340" y="1983740"/>
+              <a:ext cx="1905000" cy="2794000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6520,7 +8455,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C6B919A6-CE7A-4FA8-A762-3B62AC98807B}" name="PivotTable15" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C6B919A6-CE7A-4FA8-A762-3B62AC98807B}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -6557,9 +8492,9 @@
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="4">
         <item h="1" x="3"/>
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item h="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
       </items>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
@@ -6625,7 +8560,7 @@
       <x/>
     </i>
     <i>
-      <x v="2"/>
+      <x v="1"/>
     </i>
     <i>
       <x v="3"/>
@@ -6649,7 +8584,7 @@
   <dataFields count="1">
     <dataField name="Sum of Net Revenue" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="10">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -6671,6 +8606,99 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -6685,7 +8713,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{831FCA23-0CC0-4172-8087-CCF41D5CF4D3}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{831FCA23-0CC0-4172-8087-CCF41D5CF4D3}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -6864,9 +8892,9 @@
     <tabular pivotCacheId="306945857">
       <items count="4">
         <i x="3"/>
-        <i x="0" s="1"/>
+        <i x="0"/>
         <i x="2"/>
-        <i x="1"/>
+        <i x="1" s="1"/>
       </items>
     </tabular>
   </data>
@@ -6885,21 +8913,27 @@
 </slicers>
 </file>
 
+<file path=xl/slicers/slicer3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Region 2" xr10:uid="{54E8E100-53D3-4195-8769-F42BBFAAA855}" cache="Slicer_Region1" caption="Region" rowHeight="234950"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FFE5630F-BF6E-474F-8F2E-D9DE4F1F8824}" name="Table1" displayName="Table1" ref="A1:J51" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FFE5630F-BF6E-474F-8F2E-D9DE4F1F8824}" name="Table1" displayName="Table1" ref="A1:J51" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="A1:J51" xr:uid="{FFE5630F-BF6E-474F-8F2E-D9DE4F1F8824}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{390D635B-CA7D-421C-8626-AD1E48DA6450}" name="Order ID" dataDxfId="9" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{57D6D16B-FF12-4445-A07D-7DD5800B92F3}" name="Date " dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{AC71CADC-B12F-43BA-B984-E848C34E850E}" name="Product" dataDxfId="7" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{BF46F038-B0C0-4EB1-A544-DA774F1FD0DA}" name="Region" dataDxfId="6" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{4C8C9B52-3288-4F76-8B17-9AB851C4F868}" name="Salesperson" dataDxfId="5" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{761772D1-9B3E-41BA-BC03-B06910B94197}" name="Units" dataDxfId="4" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{57C503EC-4F3F-483D-B2C2-4C5DC35C4DD2}" name="Price(₹)" dataDxfId="3" dataCellStyle="Normal 2"/>
-    <tableColumn id="8" xr3:uid="{CE56541C-A174-4CD8-9DA7-583CD15EFA94}" name="Revenue(₹)" dataDxfId="2" dataCellStyle="Normal 2">
+    <tableColumn id="1" xr3:uid="{390D635B-CA7D-421C-8626-AD1E48DA6450}" name="Order ID" dataDxfId="8" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{57D6D16B-FF12-4445-A07D-7DD5800B92F3}" name="Date " dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{AC71CADC-B12F-43BA-B984-E848C34E850E}" name="Product" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{BF46F038-B0C0-4EB1-A544-DA774F1FD0DA}" name="Region" dataDxfId="5" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{4C8C9B52-3288-4F76-8B17-9AB851C4F868}" name="Salesperson" dataDxfId="4" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{761772D1-9B3E-41BA-BC03-B06910B94197}" name="Units" dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{57C503EC-4F3F-483D-B2C2-4C5DC35C4DD2}" name="Price(₹)" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{CE56541C-A174-4CD8-9DA7-583CD15EFA94}" name="Revenue(₹)" dataDxfId="1" dataCellStyle="Normal 2">
       <calculatedColumnFormula>F2*G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{AA8AB559-4D88-4E89-801E-80FC0E10F509}" name="Discount(%) " dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{AA8AB559-4D88-4E89-801E-80FC0E10F509}" name="Discount(%) " dataDxfId="0"/>
     <tableColumn id="10" xr3:uid="{75950157-B71A-456E-83D5-AAB312C741C3}" name="Net Revenue">
       <calculatedColumnFormula>H2*(1-I2)</calculatedColumnFormula>
     </tableColumn>
@@ -7203,6 +9237,83 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="5">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C8EE0604-9750-4267-8560-869ADD30A6C6}">
+  <we:reference id="wa200005502" version="1.0.0.13" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200005502" version="1.0.0.13" store="wa200005502" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="docId" value="&quot;q9WN6UQ7WhpCH2eSRUy4h&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CREATE_PROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{8A770647-0F8F-4790-B9ED-7A558222D104}">
+  <we:reference id="wa200005171" version="1.0.0.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200005171" version="1.0.0.0" store="wa200005171" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT_GPTINTERACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_GPTPROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_GPTPREDICT</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B2C97C3-216A-4BE1-82FF-40240E347D25}">
   <dimension ref="A1:L53"/>
@@ -7222,40 +9333,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="18"/>
+      <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
@@ -8999,9 +11110,24 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="K1:L1"/>
   </mergeCells>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{91C159BF-E5DB-4F2F-8216-8501A7FA778F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3" xr:uid="{2DF9496E-9630-46E0-B065-40B7C6DE0E77}">
       <formula1>$K$9:$K$16</formula1>
@@ -9011,6 +11137,23 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{91C159BF-E5DB-4F2F-8216-8501A7FA778F}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -9019,7 +11162,7 @@
   <dimension ref="A3:B10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9035,56 +11178,56 @@
       <c r="A4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="16">
-        <v>735265.53099999996</v>
+      <c r="B4" s="24">
+        <v>101904.72</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="16">
-        <v>710439.80149999994</v>
+        <v>43</v>
+      </c>
+      <c r="B5" s="24">
+        <v>59448.152499999997</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="16">
-        <v>479394.96600000001</v>
+      <c r="B6" s="24">
+        <v>23085.599999999999</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="16">
-        <v>465530.99349999998</v>
+      <c r="B7" s="24">
+        <v>60581.993999999999</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="16">
-        <v>496676.63049999997</v>
+      <c r="B8" s="24">
+        <v>156457.41899999999</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="16">
-        <v>51001.686499999996</v>
+      <c r="B9" s="24">
+        <v>99288.382000000012</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="16">
-        <v>463763.58</v>
+      <c r="B10" s="24">
+        <v>151079</v>
       </c>
     </row>
   </sheetData>
@@ -9220,4 +11363,121 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F11E061-DAE7-433E-A7A6-9B3E7F481003}">
+  <dimension ref="B1:O5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.77734375" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" customWidth="1"/>
+    <col min="7" max="7" width="4.6640625" customWidth="1"/>
+    <col min="8" max="8" width="3.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" customWidth="1"/>
+    <col min="10" max="10" width="3.33203125" customWidth="1"/>
+    <col min="11" max="11" width="6.5546875" customWidth="1"/>
+    <col min="12" max="12" width="4.109375" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="B1" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="G3" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="L3" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="19">
+        <f>SUM('Sales Data'!H:H)</f>
+        <v>13999086.940000005</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="G4" s="20">
+        <f>COUNTA('Sales Data'!A:A)-1</f>
+        <v>50</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="L4" s="21" t="str">
+        <f>INDEX('Sales Data'!C2:C51, MATCH(MAX('Sales Data'!H2:H51),'Sales Data'!H2:H51,0))</f>
+        <v>Laptop</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E5"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J5"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="L4:O5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
 </file>